--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
@@ -5,11 +5,11 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\重庆\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12435"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
     <sheet name="数据" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="93" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -611,17 +611,16 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:T1"/>
+  <dimension ref="A1:S1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.125" customWidth="1"/>
     <col min="2" max="13" width="14.625" customWidth="1"/>
     <col min="14" max="14" width="33" customWidth="1"/>
-    <col min="15" max="15" width="24.875" customWidth="1"/>
-    <col min="16" max="20" width="14.625" customWidth="1"/>
+    <col min="15" max="19" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:20" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -665,21 +664,18 @@
         <v>67</v>
       </c>
       <c r="O1" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="P1" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="Q1" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="R1" t="s">
-        <v>14</v>
+        <v>79</v>
       </c>
       <c r="S1" t="s">
-        <v>79</v>
-      </c>
-      <c r="T1" t="s">
         <v>15</v>
       </c>
     </row>
@@ -688,7 +684,7 @@
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{CCE6A557-97BC-4b89-ADB6-D9C93CAAB3DF}">
-      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="7">
+      <x14:dataValidations xmlns:xm="http://schemas.microsoft.com/office/excel/2006/main" count="6">
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$G$2:$G$31</xm:f>
@@ -716,12 +712,6 @@
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
             <xm:f>参考格式!$Q$2:$Q$7</xm:f>
-          </x14:formula1>
-          <xm:sqref>P2:P101</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>参考格式!$P$2:$P$6</xm:f>
           </x14:formula1>
           <xm:sqref>O2:O101</xm:sqref>
         </x14:dataValidation>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
@@ -5,7 +5,7 @@
   <workbookPr defaultThemeVersion="153222"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Administrator\Desktop\重庆\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="E:\IdeaProjects\CQ-TZJY-0930\tams\tams-invest-parent\tams-invest-entrust\src\main\resources\tpl\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
@@ -181,15 +181,6 @@
     <t>02:T+1</t>
   </si>
   <si>
-    <t>AC:摊余成本类</t>
-  </si>
-  <si>
-    <t>FVOCI:公允价值变动计入其他综合收益</t>
-  </si>
-  <si>
-    <t>FVTPL:公允价值变动计入当期损益</t>
-  </si>
-  <si>
     <t>PRM01:指定价格</t>
   </si>
   <si>
@@ -281,6 +272,18 @@
   </si>
   <si>
     <t>交易对手</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>AC:以收取该金融资产合同现金流量为目的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FVOCI:以收取该合同现金流量及出售金融资产为目的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>FVTPL:以出售该金融资产为目的</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -634,7 +637,7 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F1" t="s">
         <v>5</v>
@@ -643,7 +646,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="I1" t="s">
         <v>10</v>
@@ -652,19 +655,19 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
+        <v>62</v>
+      </c>
+      <c r="L1" t="s">
+        <v>74</v>
+      </c>
+      <c r="M1" t="s">
+        <v>63</v>
+      </c>
+      <c r="N1" t="s">
+        <v>64</v>
+      </c>
+      <c r="O1" t="s">
         <v>65</v>
-      </c>
-      <c r="L1" t="s">
-        <v>77</v>
-      </c>
-      <c r="M1" t="s">
-        <v>66</v>
-      </c>
-      <c r="N1" t="s">
-        <v>67</v>
-      </c>
-      <c r="O1" t="s">
-        <v>68</v>
       </c>
       <c r="P1" t="s">
         <v>13</v>
@@ -673,7 +676,7 @@
         <v>14</v>
       </c>
       <c r="R1" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="S1" t="s">
         <v>15</v>
@@ -777,13 +780,13 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
       <c r="L1" t="s">
+        <v>72</v>
+      </c>
+      <c r="M1" t="s">
         <v>75</v>
-      </c>
-      <c r="M1" t="s">
-        <v>78</v>
       </c>
       <c r="N1" t="s">
         <v>10</v>
@@ -792,7 +795,7 @@
         <v>11</v>
       </c>
       <c r="P1" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="Q1" t="s">
         <v>12</v>
@@ -804,7 +807,7 @@
         <v>14</v>
       </c>
       <c r="T1" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="U1" t="s">
         <v>15</v>
@@ -818,19 +821,19 @@
         <v>16</v>
       </c>
       <c r="I2" t="s">
-        <v>54</v>
+        <v>51</v>
       </c>
       <c r="N2" t="s">
         <v>49</v>
       </c>
       <c r="O2" t="s">
-        <v>51</v>
+        <v>78</v>
       </c>
       <c r="P2" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="Q2" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
     </row>
     <row r="3" spans="1:21" x14ac:dyDescent="0.15">
@@ -841,19 +844,19 @@
         <v>17</v>
       </c>
       <c r="I3" t="s">
-        <v>55</v>
+        <v>52</v>
       </c>
       <c r="N3" t="s">
         <v>50</v>
       </c>
       <c r="O3" t="s">
-        <v>52</v>
+        <v>79</v>
       </c>
       <c r="P3" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="Q3" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
     </row>
     <row r="4" spans="1:21" x14ac:dyDescent="0.15">
@@ -864,16 +867,16 @@
         <v>18</v>
       </c>
       <c r="I4" t="s">
+        <v>53</v>
+      </c>
+      <c r="O4" t="s">
+        <v>80</v>
+      </c>
+      <c r="P4" t="s">
+        <v>69</v>
+      </c>
+      <c r="Q4" t="s">
         <v>56</v>
-      </c>
-      <c r="O4" t="s">
-        <v>53</v>
-      </c>
-      <c r="P4" t="s">
-        <v>72</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>59</v>
       </c>
     </row>
     <row r="5" spans="1:21" x14ac:dyDescent="0.15">
@@ -881,10 +884,10 @@
         <v>19</v>
       </c>
       <c r="P5" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="Q5" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
     </row>
     <row r="6" spans="1:21" x14ac:dyDescent="0.15">
@@ -892,10 +895,10 @@
         <v>20</v>
       </c>
       <c r="P6" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="Q6" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
     </row>
     <row r="7" spans="1:21" x14ac:dyDescent="0.15">
@@ -903,7 +906,7 @@
         <v>21</v>
       </c>
       <c r="Q7" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
     </row>
     <row r="8" spans="1:21" x14ac:dyDescent="0.15">

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
@@ -212,10 +212,6 @@
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
-    <t>券面总额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
     <t>净价</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
@@ -284,6 +280,10 @@
   </si>
   <si>
     <t>FVTPL:以出售该金融资产为目的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>券面总额（万元）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
 </sst>
@@ -618,7 +618,9 @@
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.125" customWidth="1"/>
-    <col min="2" max="13" width="14.625" customWidth="1"/>
+    <col min="2" max="7" width="14.625" customWidth="1"/>
+    <col min="8" max="8" width="17" customWidth="1"/>
+    <col min="9" max="13" width="14.625" customWidth="1"/>
     <col min="14" max="14" width="33" customWidth="1"/>
     <col min="15" max="19" width="14.625" customWidth="1"/>
   </cols>
@@ -646,7 +648,7 @@
         <v>6</v>
       </c>
       <c r="H1" t="s">
-        <v>61</v>
+        <v>80</v>
       </c>
       <c r="I1" t="s">
         <v>10</v>
@@ -655,19 +657,19 @@
         <v>8</v>
       </c>
       <c r="K1" t="s">
+        <v>61</v>
+      </c>
+      <c r="L1" t="s">
+        <v>73</v>
+      </c>
+      <c r="M1" t="s">
         <v>62</v>
       </c>
-      <c r="L1" t="s">
-        <v>74</v>
-      </c>
-      <c r="M1" t="s">
+      <c r="N1" t="s">
         <v>63</v>
       </c>
-      <c r="N1" t="s">
+      <c r="O1" t="s">
         <v>64</v>
-      </c>
-      <c r="O1" t="s">
-        <v>65</v>
       </c>
       <c r="P1" t="s">
         <v>13</v>
@@ -676,7 +678,7 @@
         <v>14</v>
       </c>
       <c r="R1" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="S1" t="s">
         <v>15</v>
@@ -780,13 +782,13 @@
         <v>9</v>
       </c>
       <c r="K1" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="L1" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="M1" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="N1" t="s">
         <v>10</v>
@@ -795,7 +797,7 @@
         <v>11</v>
       </c>
       <c r="P1" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="Q1" t="s">
         <v>12</v>
@@ -807,7 +809,7 @@
         <v>14</v>
       </c>
       <c r="T1" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="U1" t="s">
         <v>15</v>
@@ -827,10 +829,10 @@
         <v>49</v>
       </c>
       <c r="O2" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="P2" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="Q2" t="s">
         <v>54</v>
@@ -850,10 +852,10 @@
         <v>50</v>
       </c>
       <c r="O3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="P3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="Q3" t="s">
         <v>55</v>
@@ -870,10 +872,10 @@
         <v>53</v>
       </c>
       <c r="O4" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="P4" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="Q4" t="s">
         <v>56</v>
@@ -884,7 +886,7 @@
         <v>19</v>
       </c>
       <c r="P5" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="Q5" t="s">
         <v>57</v>
@@ -895,7 +897,7 @@
         <v>20</v>
       </c>
       <c r="P6" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="Q6" t="s">
         <v>58</v>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="数据" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="92" uniqueCount="81">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -40,230 +40,180 @@
     <t>组合代码</t>
   </si>
   <si>
+    <t>交易方向</t>
+  </si>
+  <si>
+    <t>币种</t>
+  </si>
+  <si>
+    <t>价格模式</t>
+  </si>
+  <si>
+    <t>清算速度</t>
+  </si>
+  <si>
+    <t>证券账户</t>
+  </si>
+  <si>
+    <t>通道</t>
+  </si>
+  <si>
+    <t>备注</t>
+  </si>
+  <si>
+    <t>CNY:人民币（cny）</t>
+  </si>
+  <si>
+    <t>HKD:港元（hkd）</t>
+  </si>
+  <si>
+    <t>USD:美元（usd）</t>
+  </si>
+  <si>
+    <t>EUR:欧元（eur）</t>
+  </si>
+  <si>
+    <t>JPY:日元（jpy）</t>
+  </si>
+  <si>
+    <t>MOP:澳门元（mop）</t>
+  </si>
+  <si>
+    <t>CHF:瑞士法郎（chf）</t>
+  </si>
+  <si>
+    <t>GBP:英镑（gbp）</t>
+  </si>
+  <si>
+    <t>RUB:俄罗斯卢布（rub）</t>
+  </si>
+  <si>
+    <t>CAD:加拿大元（cad）</t>
+  </si>
+  <si>
+    <t>DKK:丹麦克朗（dkk）</t>
+  </si>
+  <si>
+    <t>AUD:澳大利亚元（aud）</t>
+  </si>
+  <si>
+    <t>SEK:瑞典克朗（sek）</t>
+  </si>
+  <si>
+    <t>SGD:新加坡元（sgd）</t>
+  </si>
+  <si>
+    <t>TWD:新台币（twd）</t>
+  </si>
+  <si>
+    <t>AED:阿联酋迪拉姆(aed)</t>
+  </si>
+  <si>
+    <t>HUF:匈牙利福林(huf)</t>
+  </si>
+  <si>
+    <t>KHR:柬埔寨瑞尔(khr)</t>
+  </si>
+  <si>
+    <t>KRW:韩元(krw)</t>
+  </si>
+  <si>
+    <t>KZT:哈萨克斯坦坚戈(kzt)</t>
+  </si>
+  <si>
+    <t>MNT:蒙古图格里克 (mnt)</t>
+  </si>
+  <si>
+    <t>MXN:墨西哥元(mxn)</t>
+  </si>
+  <si>
+    <t>MYR:马来西亚林吉特(myr)</t>
+  </si>
+  <si>
+    <t>NOK:挪威克朗(nok)</t>
+  </si>
+  <si>
+    <t>NZD:新西兰元(nzd)</t>
+  </si>
+  <si>
+    <t>PLN:波兰兹罗提(pln)</t>
+  </si>
+  <si>
+    <t>SAR:沙特里亚尔(sar)</t>
+  </si>
+  <si>
+    <t>THB:泰铢(thb)</t>
+  </si>
+  <si>
+    <t>TRY:新土耳其里拉(try)</t>
+  </si>
+  <si>
+    <t>ZAR:南非兰特(zar)</t>
+  </si>
+  <si>
+    <t>T01:买入</t>
+  </si>
+  <si>
+    <t>T02:卖出</t>
+  </si>
+  <si>
+    <t>T03:行权-回售</t>
+  </si>
+  <si>
+    <t>01:T+0</t>
+  </si>
+  <si>
+    <t>02:T+1</t>
+  </si>
+  <si>
+    <t>PRM01:指定价格</t>
+  </si>
+  <si>
+    <t>PRM02:限价指令</t>
+  </si>
+  <si>
+    <t>PRM03:市价指令</t>
+  </si>
+  <si>
+    <t>01:外汇交易中心</t>
+  </si>
+  <si>
+    <t>02:竞价撮合平台</t>
+  </si>
+  <si>
+    <t>03:固定收益平台</t>
+  </si>
+  <si>
+    <t>04:大宗交易平台</t>
+  </si>
+  <si>
+    <t>05:综合协议平台</t>
+  </si>
+  <si>
+    <t>99:其它</t>
+  </si>
+  <si>
     <t>资产代码</t>
-  </si>
-  <si>
-    <t>交易方向</t>
-  </si>
-  <si>
-    <t>币种</t>
-  </si>
-  <si>
-    <t>券面总额</t>
-  </si>
-  <si>
-    <t>价格模式</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>净价</t>
-  </si>
-  <si>
-    <t>清算速度</t>
+    <phoneticPr fontId="1" type="noConversion"/>
+  </si>
+  <si>
+    <t>到期收益率（%）</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>投资目的</t>
+    <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>交易平台</t>
-  </si>
-  <si>
-    <t>证券账户</t>
-  </si>
-  <si>
-    <t>通道</t>
-  </si>
-  <si>
-    <t>备注</t>
-  </si>
-  <si>
-    <t>CNY:人民币（cny）</t>
-  </si>
-  <si>
-    <t>HKD:港元（hkd）</t>
-  </si>
-  <si>
-    <t>USD:美元（usd）</t>
-  </si>
-  <si>
-    <t>EUR:欧元（eur）</t>
-  </si>
-  <si>
-    <t>JPY:日元（jpy）</t>
-  </si>
-  <si>
-    <t>MOP:澳门元（mop）</t>
-  </si>
-  <si>
-    <t>CHF:瑞士法郎（chf）</t>
-  </si>
-  <si>
-    <t>GBP:英镑（gbp）</t>
-  </si>
-  <si>
-    <t>RUB:俄罗斯卢布（rub）</t>
-  </si>
-  <si>
-    <t>CAD:加拿大元（cad）</t>
-  </si>
-  <si>
-    <t>DKK:丹麦克朗（dkk）</t>
-  </si>
-  <si>
-    <t>AUD:澳大利亚元（aud）</t>
-  </si>
-  <si>
-    <t>SEK:瑞典克朗（sek）</t>
-  </si>
-  <si>
-    <t>SGD:新加坡元（sgd）</t>
-  </si>
-  <si>
-    <t>TWD:新台币（twd）</t>
-  </si>
-  <si>
-    <t>AED:阿联酋迪拉姆(aed)</t>
-  </si>
-  <si>
-    <t>HUF:匈牙利福林(huf)</t>
-  </si>
-  <si>
-    <t>KHR:柬埔寨瑞尔(khr)</t>
-  </si>
-  <si>
-    <t>KRW:韩元(krw)</t>
-  </si>
-  <si>
-    <t>KZT:哈萨克斯坦坚戈(kzt)</t>
-  </si>
-  <si>
-    <t>MNT:蒙古图格里克 (mnt)</t>
-  </si>
-  <si>
-    <t>MXN:墨西哥元(mxn)</t>
-  </si>
-  <si>
-    <t>MYR:马来西亚林吉特(myr)</t>
-  </si>
-  <si>
-    <t>NOK:挪威克朗(nok)</t>
-  </si>
-  <si>
-    <t>NZD:新西兰元(nzd)</t>
-  </si>
-  <si>
-    <t>PLN:波兰兹罗提(pln)</t>
-  </si>
-  <si>
-    <t>SAR:沙特里亚尔(sar)</t>
-  </si>
-  <si>
-    <t>THB:泰铢(thb)</t>
-  </si>
-  <si>
-    <t>TRY:新土耳其里拉(try)</t>
-  </si>
-  <si>
-    <t>ZAR:南非兰特(zar)</t>
-  </si>
-  <si>
-    <t>T01:买入</t>
-  </si>
-  <si>
-    <t>T02:卖出</t>
-  </si>
-  <si>
-    <t>T03:行权-回售</t>
-  </si>
-  <si>
-    <t>01:T+0</t>
-  </si>
-  <si>
-    <t>02:T+1</t>
-  </si>
-  <si>
-    <t>PRM01:指定价格</t>
-  </si>
-  <si>
-    <t>PRM02:限价指令</t>
-  </si>
-  <si>
-    <t>PRM03:市价指令</t>
-  </si>
-  <si>
-    <t>01:外汇交易中心</t>
-  </si>
-  <si>
-    <t>02:竞价撮合平台</t>
-  </si>
-  <si>
-    <t>03:固定收益平台</t>
-  </si>
-  <si>
-    <t>04:大宗交易平台</t>
-  </si>
-  <si>
-    <t>05:综合协议平台</t>
-  </si>
-  <si>
-    <t>99:其它</t>
-  </si>
-  <si>
-    <t>资产代码</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>净价</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>到期收益率（%）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>投资目的</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易平台</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t xml:space="preserve">交易场所 </t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>01:银行间</t>
-  </si>
-  <si>
-    <t>03:上海证券交易所</t>
-  </si>
-  <si>
-    <t>04:深圳证券交易所</t>
-  </si>
-  <si>
-    <t>05:机构间私募系统</t>
-  </si>
-  <si>
-    <t>09:OTC场外</t>
-  </si>
-  <si>
-    <t>到期收益率（%）</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
     <t>行权收益率（%）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>行权收益率（%）</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>最低成交金额</t>
-    <phoneticPr fontId="1" type="noConversion"/>
-  </si>
-  <si>
-    <t>交易对手</t>
     <phoneticPr fontId="1" type="noConversion"/>
   </si>
   <si>
@@ -639,49 +589,49 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" t="s">
+        <v>4</v>
+      </c>
+      <c r="G1" t="s">
+        <v>5</v>
+      </c>
+      <c r="H1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
+        <v>6</v>
+      </c>
+      <c r="K1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" t="s">
         <v>60</v>
       </c>
-      <c r="F1" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" t="s">
-        <v>80</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
+        <v>8</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>9</v>
+      </c>
+      <c r="R1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S1" t="s">
         <v>10</v>
-      </c>
-      <c r="J1" t="s">
-        <v>8</v>
-      </c>
-      <c r="K1" t="s">
-        <v>61</v>
-      </c>
-      <c r="L1" t="s">
-        <v>73</v>
-      </c>
-      <c r="M1" t="s">
-        <v>62</v>
-      </c>
-      <c r="N1" t="s">
-        <v>63</v>
-      </c>
-      <c r="O1" t="s">
-        <v>64</v>
-      </c>
-      <c r="P1" t="s">
-        <v>13</v>
-      </c>
-      <c r="Q1" t="s">
-        <v>14</v>
-      </c>
-      <c r="R1" t="s">
-        <v>75</v>
-      </c>
-      <c r="S1" t="s">
-        <v>15</v>
       </c>
     </row>
   </sheetData>
@@ -698,33 +648,33 @@
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>参考格式!$I$2:$I$4</xm:f>
+            <xm:f>参考格式!$F$2:$F$4</xm:f>
+          </x14:formula1>
+          <xm:sqref>F2:F101</xm:sqref>
+        </x14:dataValidation>
+        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
+          <x14:formula1>
+            <xm:f>参考格式!$J$2:$J$4</xm:f>
           </x14:formula1>
           <xm:sqref>J2:J101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>参考格式!$N$2:$N$3</xm:f>
+            <xm:f>参考格式!$I$2:$I$3</xm:f>
           </x14:formula1>
           <xm:sqref>I2:I101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>参考格式!$O$2:$O$4</xm:f>
+            <xm:f>参考格式!$N$2:$N$4</xm:f>
           </x14:formula1>
           <xm:sqref>N2:N101</xm:sqref>
         </x14:dataValidation>
         <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
           <x14:formula1>
-            <xm:f>参考格式!$Q$2:$Q$7</xm:f>
+            <xm:f>参考格式!$O$2:$O$7</xm:f>
           </x14:formula1>
           <xm:sqref>O2:O101</xm:sqref>
-        </x14:dataValidation>
-        <x14:dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1">
-          <x14:formula1>
-            <xm:f>参考格式!$F$2:$F$4</xm:f>
-          </x14:formula1>
-          <xm:sqref>F2:F101</xm:sqref>
         </x14:dataValidation>
       </x14:dataValidations>
     </ext>
@@ -734,7 +684,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:U31"/>
+  <dimension ref="A1:S31"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="3" width="17.875" bestFit="1" customWidth="1"/>
@@ -742,15 +692,15 @@
     <col min="7" max="7" width="25.125" bestFit="1" customWidth="1"/>
     <col min="9" max="9" width="15.5" bestFit="1" customWidth="1"/>
     <col min="11" max="12" width="16.25" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="16.25" customWidth="1"/>
-    <col min="15" max="15" width="36.375" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="16.25" customWidth="1"/>
+    <col min="15" max="15" width="21.625" customWidth="1"/>
     <col min="16" max="16" width="30.625" customWidth="1"/>
     <col min="17" max="17" width="16.375" bestFit="1" customWidth="1"/>
     <col min="20" max="20" width="14.25" customWidth="1"/>
     <col min="21" max="22" width="13" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:21" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -764,271 +714,250 @@
         <v>3</v>
       </c>
       <c r="E1" t="s">
+        <v>55</v>
+      </c>
+      <c r="F1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="G1" t="s">
         <v>5</v>
       </c>
-      <c r="G1" t="s">
+      <c r="H1" t="s">
+        <v>65</v>
+      </c>
+      <c r="I1" t="s">
+        <v>7</v>
+      </c>
+      <c r="J1" t="s">
         <v>6</v>
       </c>
-      <c r="H1" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" t="s">
+      <c r="K1" t="s">
+        <v>56</v>
+      </c>
+      <c r="L1" t="s">
+        <v>60</v>
+      </c>
+      <c r="M1" t="s">
+        <v>57</v>
+      </c>
+      <c r="N1" t="s">
+        <v>58</v>
+      </c>
+      <c r="O1" t="s">
+        <v>59</v>
+      </c>
+      <c r="P1" t="s">
         <v>8</v>
       </c>
-      <c r="J1" t="s">
+      <c r="Q1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" t="s">
-        <v>72</v>
-      </c>
-      <c r="L1" t="s">
-        <v>71</v>
-      </c>
-      <c r="M1" t="s">
-        <v>74</v>
-      </c>
-      <c r="N1" t="s">
+      <c r="R1" t="s">
+        <v>61</v>
+      </c>
+      <c r="S1" t="s">
         <v>10</v>
       </c>
-      <c r="O1" t="s">
+    </row>
+    <row r="2" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="F2" t="s">
+        <v>41</v>
+      </c>
+      <c r="G2" t="s">
         <v>11</v>
       </c>
-      <c r="P1" t="s">
-        <v>65</v>
-      </c>
-      <c r="Q1" t="s">
+      <c r="I2" t="s">
+        <v>44</v>
+      </c>
+      <c r="J2" t="s">
+        <v>46</v>
+      </c>
+      <c r="N2" t="s">
+        <v>62</v>
+      </c>
+      <c r="O2" t="s">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="3" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="F3" t="s">
+        <v>42</v>
+      </c>
+      <c r="G3" t="s">
         <v>12</v>
       </c>
-      <c r="R1" t="s">
+      <c r="I3" t="s">
+        <v>45</v>
+      </c>
+      <c r="J3" t="s">
+        <v>47</v>
+      </c>
+      <c r="N3" t="s">
+        <v>63</v>
+      </c>
+      <c r="O3" t="s">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="4" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="F4" t="s">
+        <v>43</v>
+      </c>
+      <c r="G4" t="s">
         <v>13</v>
       </c>
-      <c r="S1" t="s">
+      <c r="J4" t="s">
+        <v>48</v>
+      </c>
+      <c r="N4" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" t="s">
+        <v>51</v>
+      </c>
+    </row>
+    <row r="5" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G5" t="s">
         <v>14</v>
       </c>
-      <c r="T1" t="s">
-        <v>76</v>
-      </c>
-      <c r="U1" t="s">
+      <c r="O5" t="s">
+        <v>52</v>
+      </c>
+    </row>
+    <row r="6" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G6" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="2" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="F2" t="s">
-        <v>46</v>
-      </c>
-      <c r="G2" t="s">
+      <c r="O6" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G7" t="s">
         <v>16</v>
       </c>
-      <c r="I2" t="s">
-        <v>51</v>
-      </c>
-      <c r="N2" t="s">
-        <v>49</v>
-      </c>
-      <c r="O2" t="s">
-        <v>77</v>
-      </c>
-      <c r="P2" t="s">
-        <v>66</v>
-      </c>
-      <c r="Q2" t="s">
+      <c r="O7" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="3" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="F3" t="s">
-        <v>47</v>
-      </c>
-      <c r="G3" t="s">
+    <row r="8" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G8" t="s">
         <v>17</v>
       </c>
-      <c r="I3" t="s">
-        <v>52</v>
-      </c>
-      <c r="N3" t="s">
-        <v>50</v>
-      </c>
-      <c r="O3" t="s">
-        <v>78</v>
-      </c>
-      <c r="P3" t="s">
-        <v>67</v>
-      </c>
-      <c r="Q3" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="4" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="F4" t="s">
-        <v>48</v>
-      </c>
-      <c r="G4" t="s">
+    </row>
+    <row r="9" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G9" t="s">
         <v>18</v>
       </c>
-      <c r="I4" t="s">
-        <v>53</v>
-      </c>
-      <c r="O4" t="s">
-        <v>79</v>
-      </c>
-      <c r="P4" t="s">
-        <v>68</v>
-      </c>
-      <c r="Q4" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="5" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G5" t="s">
+    </row>
+    <row r="10" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G10" t="s">
         <v>19</v>
       </c>
-      <c r="P5" t="s">
-        <v>69</v>
-      </c>
-      <c r="Q5" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="6" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G6" t="s">
+    </row>
+    <row r="11" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G11" t="s">
         <v>20</v>
       </c>
-      <c r="P6" t="s">
-        <v>70</v>
-      </c>
-      <c r="Q6" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="7" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G7" t="s">
+    </row>
+    <row r="12" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G12" t="s">
         <v>21</v>
       </c>
-      <c r="Q7" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="8" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G8" t="s">
+    </row>
+    <row r="13" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G13" t="s">
         <v>22</v>
       </c>
     </row>
-    <row r="9" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G9" t="s">
+    <row r="14" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G14" t="s">
         <v>23</v>
       </c>
     </row>
-    <row r="10" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G10" t="s">
+    <row r="15" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G15" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="11" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G11" t="s">
+    <row r="16" spans="1:19" x14ac:dyDescent="0.15">
+      <c r="G16" t="s">
         <v>25</v>
-      </c>
-    </row>
-    <row r="12" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G12" t="s">
-        <v>26</v>
-      </c>
-    </row>
-    <row r="13" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G13" t="s">
-        <v>27</v>
-      </c>
-    </row>
-    <row r="14" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G14" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="15" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G15" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="16" spans="1:21" x14ac:dyDescent="0.15">
-      <c r="G16" t="s">
-        <v>30</v>
       </c>
     </row>
     <row r="17" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G17" t="s">
-        <v>31</v>
+        <v>26</v>
       </c>
     </row>
     <row r="18" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G18" t="s">
-        <v>32</v>
+        <v>27</v>
       </c>
     </row>
     <row r="19" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G19" t="s">
-        <v>33</v>
+        <v>28</v>
       </c>
     </row>
     <row r="20" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G20" t="s">
-        <v>34</v>
+        <v>29</v>
       </c>
     </row>
     <row r="21" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G21" t="s">
-        <v>35</v>
+        <v>30</v>
       </c>
     </row>
     <row r="22" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G22" t="s">
-        <v>36</v>
+        <v>31</v>
       </c>
     </row>
     <row r="23" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G23" t="s">
-        <v>37</v>
+        <v>32</v>
       </c>
     </row>
     <row r="24" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G24" t="s">
-        <v>38</v>
+        <v>33</v>
       </c>
     </row>
     <row r="25" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G25" t="s">
-        <v>39</v>
+        <v>34</v>
       </c>
     </row>
     <row r="26" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G26" t="s">
-        <v>40</v>
+        <v>35</v>
       </c>
     </row>
     <row r="27" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G27" t="s">
-        <v>41</v>
+        <v>36</v>
       </c>
     </row>
     <row r="28" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G28" t="s">
-        <v>42</v>
+        <v>37</v>
       </c>
     </row>
     <row r="29" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G29" t="s">
-        <v>43</v>
+        <v>38</v>
       </c>
     </row>
     <row r="30" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G30" t="s">
-        <v>44</v>
+        <v>39</v>
       </c>
     </row>
     <row r="31" spans="7:7" x14ac:dyDescent="0.15">
       <c r="G31" t="s">
-        <v>45</v>
+        <v>40</v>
       </c>
     </row>
   </sheetData>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
@@ -9,7 +9,7 @@
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755" activeTab="1"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="20490" windowHeight="7755"/>
   </bookViews>
   <sheets>
     <sheet name="数据" sheetId="1" r:id="rId1"/>

--- a/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
+++ b/tams-invest-parent/tams-invest-entrust/src/main/resources/tpl/EtrIbBondInfo004MTM.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="85" uniqueCount="66">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="83" uniqueCount="66">
   <si>
     <t>序号</t>
     <phoneticPr fontId="1" type="noConversion"/>
@@ -564,7 +564,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:S1"/>
+  <dimension ref="A1:Q1"/>
   <sheetFormatPr defaultRowHeight="13.5" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="1" max="1" width="6.125" customWidth="1"/>
@@ -572,10 +572,10 @@
     <col min="8" max="8" width="17" customWidth="1"/>
     <col min="9" max="13" width="14.625" customWidth="1"/>
     <col min="14" max="14" width="33" customWidth="1"/>
-    <col min="15" max="19" width="14.625" customWidth="1"/>
+    <col min="15" max="17" width="14.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:19" x14ac:dyDescent="0.15">
+    <row r="1" spans="1:17" x14ac:dyDescent="0.15">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -622,15 +622,9 @@
         <v>59</v>
       </c>
       <c r="P1" t="s">
-        <v>8</v>
+        <v>61</v>
       </c>
       <c r="Q1" t="s">
-        <v>9</v>
-      </c>
-      <c r="R1" t="s">
-        <v>61</v>
-      </c>
-      <c r="S1" t="s">
         <v>10</v>
       </c>
     </row>
